--- a/data/industry/TrendForce/TFT LCD.xlsx
+++ b/data/industry/TrendForce/TFT LCD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8BC208-7DAF-4E8C-A708-0F0AF6150FCB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8F6153-6392-4C99-A1B3-AD21014B50CF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16905" yWindow="780" windowWidth="19215" windowHeight="20925" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -285,13 +285,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -587,16 +587,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -646,10 +646,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="16"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="6" t="s">
         <v>25</v>
       </c>
@@ -848,16 +848,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="14" t="s">
@@ -899,10 +899,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="16"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="14" t="s">
         <v>25</v>
       </c>
@@ -1108,16 +1108,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="14" t="s">
@@ -1183,10 +1183,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="16"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="14" t="s">
         <v>25</v>
       </c>
@@ -1250,10 +1250,10 @@
       <c r="Y2" s="6"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
+      <c r="A3" s="16">
         <v>45991</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="16">
         <v>45991</v>
       </c>
       <c r="C3" s="9">
@@ -1555,16 +1555,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="12" t="s">
@@ -1610,10 +1610,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="16"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="12" t="s">
         <v>34</v>
       </c>

--- a/data/industry/TrendForce/TFT LCD.xlsx
+++ b/data/industry/TrendForce/TFT LCD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8F6153-6392-4C99-A1B3-AD21014B50CF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E741F6-BF27-448A-8EEA-16DD5C548D99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16905" yWindow="780" windowWidth="19215" windowHeight="20925" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16905" yWindow="780" windowWidth="19215" windowHeight="20925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Large Size Panel" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="36">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -815,8 +815,54 @@
       <c r="Y4" s="6"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="8">
+        <v>46104</v>
+      </c>
+      <c r="B5" s="8">
+        <v>46104</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="11">
+        <v>119</v>
+      </c>
+      <c r="F5" s="11">
+        <v>129</v>
+      </c>
+      <c r="G5" s="11">
+        <v>126</v>
+      </c>
+      <c r="H5" s="11">
+        <v>124</v>
+      </c>
+      <c r="I5" s="11">
+        <v>57.7</v>
+      </c>
+      <c r="J5" s="11">
+        <v>66</v>
+      </c>
+      <c r="K5" s="11">
+        <v>63.1</v>
+      </c>
+      <c r="L5" s="11">
+        <v>63</v>
+      </c>
+      <c r="M5" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="N5" s="11">
+        <v>27.9</v>
+      </c>
+      <c r="O5" s="11">
+        <v>26.7</v>
+      </c>
+      <c r="P5" s="11">
+        <v>26.7</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -827,6 +873,7 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/industry/TrendForce/TFT LCD.xlsx
+++ b/data/industry/TrendForce/TFT LCD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E741F6-BF27-448A-8EEA-16DD5C548D99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D4C9B0-A057-454C-ACF3-B61301B94F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16905" yWindow="780" windowWidth="19215" windowHeight="20925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Large Size Panel" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="36">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -173,24 +173,25 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -203,7 +204,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -246,11 +247,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -259,45 +260,48 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -576,27 +580,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9EFAE0-DDA9-4895-A6E7-1B8A3730BEB2}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="25" width="9" style="11"/>
+    <col min="1" max="1" width="12.08984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -645,11 +649,11 @@
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="17"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="6" t="s">
         <v>25</v>
       </c>
@@ -696,17 +700,17 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="8">
+    <row r="3" spans="1:25">
+      <c r="A3" s="18">
         <v>46042</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="18">
         <v>46042</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>0.5</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="6">
@@ -755,17 +759,17 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
+    <row r="4" spans="1:25">
+      <c r="A4" s="18">
         <v>46077</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="18">
         <v>46077</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>0.5</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="6">
@@ -814,53 +818,53 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
+    <row r="5" spans="1:25">
+      <c r="A5" s="18">
         <v>46104</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="18">
         <v>46104</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>0.5</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>119</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <v>129</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <v>126</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="10">
         <v>124</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="10">
         <v>57.7</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="10">
         <v>66</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="10">
         <v>63.1</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="10">
         <v>63</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="10">
         <v>26.2</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="10">
         <v>27.9</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="10">
         <v>26.7</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="10">
         <v>26.7</v>
       </c>
     </row>
@@ -879,56 +883,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C2B366-3BE4-4AC7-87BD-872D5D27BEBF}">
-  <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.625" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" style="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.5" style="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="25" width="9" style="11"/>
+    <col min="1" max="1" width="12.08984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.6328125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="M1" s="2"/>
@@ -945,33 +949,33 @@
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="14" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="13" t="s">
         <v>31</v>
       </c>
       <c r="M2" s="6"/>
@@ -988,41 +992,41 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="8">
+    <row r="3" spans="1:25">
+      <c r="A3" s="18">
         <v>46022</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="18">
         <v>46022</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>1.2</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="13">
         <v>1.7</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="13">
         <v>1.4</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>1.4</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>5.7</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="13">
         <v>8.5</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="13">
         <v>6.8</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="13">
         <v>6.9</v>
       </c>
       <c r="M3" s="6"/>
@@ -1039,41 +1043,41 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
+    <row r="4" spans="1:25">
+      <c r="A4" s="18">
         <v>46052</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="18">
         <v>46052</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="13">
         <v>1.2</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="13">
         <v>1.7</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="13">
         <v>1.4</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>1.4</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>5.7</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>8.5</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>6.7</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="13">
         <v>6.8</v>
       </c>
       <c r="M4" s="6"/>
@@ -1090,42 +1094,80 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
+    <row r="5" spans="1:25">
+      <c r="A5" s="18">
         <v>46079</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="18">
         <v>46079</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="14">
         <v>1.2</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="14">
         <v>1.7</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="14">
         <v>1.4</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="14">
         <v>1.4</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="14">
         <v>5.7</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="14">
         <v>8.5</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="14">
         <v>6.6</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="14">
         <v>6.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" s="18">
+        <v>46111</v>
+      </c>
+      <c r="B6" s="18">
+        <v>46111</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="F6" s="14">
+        <v>1.7</v>
+      </c>
+      <c r="G6" s="14">
+        <v>1.4</v>
+      </c>
+      <c r="H6" s="14">
+        <v>1.4</v>
+      </c>
+      <c r="I6" s="14">
+        <v>5.7</v>
+      </c>
+      <c r="J6" s="14">
+        <v>8.5</v>
+      </c>
+      <c r="K6" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="L6" s="14">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -1143,429 +1185,429 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F72FC54-CD8C-473D-B869-CF3F9FC5C7CC}">
   <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="24" width="8.875" style="15" customWidth="1"/>
-    <col min="25" max="25" width="9" style="11"/>
+    <col min="1" max="1" width="12.08984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="24" width="8.90625" style="14" customWidth="1"/>
+    <col min="25" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="S1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="14" t="s">
+      <c r="V1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="14" t="s">
+      <c r="W1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="X1" s="13" t="s">
         <v>12</v>
       </c>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="14" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="M2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="Q2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="R2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="S2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="T2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="U2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="V2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="W2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="14" t="s">
+      <c r="X2" s="13" t="s">
         <v>31</v>
       </c>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="16">
+    <row r="3" spans="1:25">
+      <c r="A3" s="19">
         <v>45991</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="19">
         <v>45991</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="13">
         <v>72</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="13">
         <v>72</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="13">
         <v>72</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14">
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13">
         <v>94</v>
       </c>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14">
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13">
         <v>297.5</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14">
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13">
         <v>395.3</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14">
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13">
         <v>160.4</v>
       </c>
-      <c r="X3" s="14"/>
+      <c r="X3" s="13"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
+    <row r="4" spans="1:25">
+      <c r="A4" s="18">
         <v>46022</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="18">
         <v>46022</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="13">
         <v>72.8</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="13">
         <v>72.8</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="13">
         <v>72.8</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>72</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>91.4</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>130</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>94.4</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="13">
         <v>94</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="13">
         <v>246.7</v>
       </c>
-      <c r="N4" s="14">
+      <c r="N4" s="13">
         <v>305.8</v>
       </c>
-      <c r="O4" s="14">
+      <c r="O4" s="13">
         <v>293.7</v>
       </c>
-      <c r="P4" s="14">
+      <c r="P4" s="13">
         <v>297.5</v>
       </c>
-      <c r="Q4" s="14">
+      <c r="Q4" s="13">
         <v>362.2</v>
       </c>
-      <c r="R4" s="14">
+      <c r="R4" s="13">
         <v>410.1</v>
       </c>
-      <c r="S4" s="14">
+      <c r="S4" s="13">
         <v>387.3</v>
       </c>
-      <c r="T4" s="14">
+      <c r="T4" s="13">
         <v>395.3</v>
       </c>
-      <c r="U4" s="14">
+      <c r="U4" s="13">
         <v>149.19999999999999</v>
       </c>
-      <c r="V4" s="14">
+      <c r="V4" s="13">
         <v>195.1</v>
       </c>
-      <c r="W4" s="14">
+      <c r="W4" s="13">
         <v>160.9</v>
       </c>
-      <c r="X4" s="14">
+      <c r="X4" s="13">
         <v>160.4</v>
       </c>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
+    <row r="5" spans="1:25">
+      <c r="A5" s="18">
         <v>46052</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="18">
         <v>46052</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>73.599999999999994</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <v>73.599999999999994</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <v>73.599999999999994</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>72.8</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>94.9</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>142.30000000000001</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>96.9</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="13">
         <v>64.400000000000006</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="13">
         <v>210</v>
       </c>
-      <c r="N5" s="14">
+      <c r="N5" s="13">
         <v>309.3</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="13">
         <v>283.3</v>
       </c>
-      <c r="P5" s="14">
+      <c r="P5" s="13">
         <v>293.7</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="Q5" s="13">
         <v>375</v>
       </c>
-      <c r="R5" s="14">
+      <c r="R5" s="13">
         <v>413.8</v>
       </c>
-      <c r="S5" s="14">
+      <c r="S5" s="13">
         <v>391.2</v>
       </c>
-      <c r="T5" s="14">
+      <c r="T5" s="13">
         <v>387.3</v>
       </c>
-      <c r="U5" s="14">
+      <c r="U5" s="13">
         <v>149.80000000000001</v>
       </c>
-      <c r="V5" s="14">
+      <c r="V5" s="13">
         <v>193.2</v>
       </c>
-      <c r="W5" s="14">
+      <c r="W5" s="13">
         <v>161.9</v>
       </c>
-      <c r="X5" s="14">
+      <c r="X5" s="13">
         <v>160.9</v>
       </c>
       <c r="Y5" s="6"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A6" s="8">
+    <row r="6" spans="1:25">
+      <c r="A6" s="18">
         <v>46079</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="18">
         <v>46079</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="14">
         <v>74.2</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="14">
         <v>74.2</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="14">
         <v>74.2</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="14">
         <v>73.599999999999994</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="14">
         <v>97.3</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="14">
         <v>144.80000000000001</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="14">
         <v>99.4</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="14">
         <v>96.9</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="14">
         <v>199.4</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="14">
         <v>326</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="14">
         <v>298.10000000000002</v>
       </c>
-      <c r="P6" s="15">
+      <c r="P6" s="14">
         <v>283.3</v>
       </c>
-      <c r="Q6" s="15">
+      <c r="Q6" s="14">
         <v>376.4</v>
       </c>
-      <c r="R6" s="15">
+      <c r="R6" s="14">
         <v>418.4</v>
       </c>
-      <c r="S6" s="15">
+      <c r="S6" s="14">
         <v>406.3</v>
       </c>
-      <c r="T6" s="15">
+      <c r="T6" s="14">
         <v>391.2</v>
       </c>
-      <c r="U6" s="15">
+      <c r="U6" s="14">
         <v>152</v>
       </c>
-      <c r="V6" s="15">
+      <c r="V6" s="14">
         <v>199.1</v>
       </c>
-      <c r="W6" s="15">
+      <c r="W6" s="14">
         <v>161.80000000000001</v>
       </c>
-      <c r="X6" s="15">
+      <c r="X6" s="14">
         <v>161.9</v>
       </c>
     </row>
@@ -1583,65 +1625,65 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535C5E87-C6BF-4E93-9B61-00AC746AD42A}">
-  <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="13"/>
-    <col min="7" max="7" width="11.625" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.625" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="11.625" style="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="25" width="9" style="11"/>
+    <col min="1" max="1" width="12.08984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.453125" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="11" t="s">
         <v>33</v>
       </c>
       <c r="O1" s="2"/>
@@ -1656,39 +1698,39 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="12" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="11" t="s">
         <v>35</v>
       </c>
       <c r="O2" s="6"/>
@@ -1703,45 +1745,44 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="8">
+    <row r="3" spans="1:25">
+      <c r="A3" s="18">
         <v>45962</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>24118</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="11">
         <v>738</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <v>18186</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>1184</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <v>13817</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="11">
         <v>2638</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="11">
         <v>20226</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="11">
         <v>15428</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="11">
         <v>76347</v>
       </c>
-      <c r="N3" s="12">
+      <c r="N3" s="11">
         <v>19987</v>
       </c>
       <c r="O3" s="6"/>
@@ -1756,47 +1797,47 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
+    <row r="4" spans="1:25">
+      <c r="A4" s="18">
         <v>45992</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="18">
         <v>46042</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>26154</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>786</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>20229</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>1306</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>14924</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>2849</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <v>21536</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="11">
         <v>16649</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="11">
         <v>82844</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="11">
         <v>21591</v>
       </c>
       <c r="O4" s="6"/>
@@ -1811,48 +1852,92 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
+    <row r="5" spans="1:25">
+      <c r="A5" s="18">
         <v>45658</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="18">
         <v>46079</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <v>21091</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>591</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>17998</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <v>1163</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <v>14139</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <v>2690</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="12">
         <v>22008</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="12">
         <v>16619</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="12">
         <v>75236</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="12">
         <v>21064</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" s="18">
+        <v>45689</v>
+      </c>
+      <c r="B6" s="18">
+        <v>46106</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="12">
+        <v>19143</v>
+      </c>
+      <c r="F6" s="12">
+        <v>552</v>
+      </c>
+      <c r="G6" s="12">
+        <v>14885</v>
+      </c>
+      <c r="H6" s="12">
+        <v>950</v>
+      </c>
+      <c r="I6" s="12">
+        <v>12274</v>
+      </c>
+      <c r="J6" s="12">
+        <v>2362</v>
+      </c>
+      <c r="K6" s="12">
+        <v>18459</v>
+      </c>
+      <c r="L6" s="12">
+        <v>14203</v>
+      </c>
+      <c r="M6" s="12">
+        <v>64762</v>
+      </c>
+      <c r="N6" s="12">
+        <v>18066</v>
       </c>
     </row>
   </sheetData>
@@ -1870,20 +1955,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1891,19 +1976,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1911,13 +1996,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1925,31 +2010,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -1957,25 +2042,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>18</v>

--- a/data/industry/TrendForce/TFT LCD.xlsx
+++ b/data/industry/TrendForce/TFT LCD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D4C9B0-A057-454C-ACF3-B61301B94F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19ED8C9-CA77-4848-B20D-14335A4E8709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Large Size Panel" sheetId="2" r:id="rId1"/>
@@ -24,12 +24,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="36">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -174,24 +177,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -204,7 +207,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -247,7 +250,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -260,48 +263,48 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -580,27 +583,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9EFAE0-DDA9-4895-A6E7-1B8A3730BEB2}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="19" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -649,11 +652,11 @@
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="6" t="s">
         <v>25</v>
       </c>
@@ -700,11 +703,11 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="18">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" s="15">
         <v>46042</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="15">
         <v>46042</v>
       </c>
       <c r="C3" s="8">
@@ -759,11 +762,11 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="18">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" s="15">
         <v>46077</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="15">
         <v>46077</v>
       </c>
       <c r="C4" s="8">
@@ -818,11 +821,11 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="18">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" s="15">
         <v>46104</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="15">
         <v>46104</v>
       </c>
       <c r="C5" s="8">
@@ -884,31 +887,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C2B366-3BE4-4AC7-87BD-872D5D27BEBF}">
   <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.6328125" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.625" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.5" style="14" bestFit="1" customWidth="1"/>
     <col min="13" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="19" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -949,11 +952,11 @@
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="13" t="s">
         <v>25</v>
       </c>
@@ -992,11 +995,11 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="18">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" s="15">
         <v>46022</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="15">
         <v>46022</v>
       </c>
       <c r="C3" s="8">
@@ -1043,11 +1046,11 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="18">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" s="15">
         <v>46052</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="15">
         <v>46052</v>
       </c>
       <c r="C4" s="8">
@@ -1094,11 +1097,11 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="18">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" s="15">
         <v>46079</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="15">
         <v>46079</v>
       </c>
       <c r="C5" s="8">
@@ -1132,11 +1135,11 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="18">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A6" s="15">
         <v>46111</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="15">
         <v>46111</v>
       </c>
       <c r="C6" s="8">
@@ -1184,29 +1187,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F72FC54-CD8C-473D-B869-CF3F9FC5C7CC}">
-  <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="24" width="8.90625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="24" width="8.875" style="14" customWidth="1"/>
     <col min="25" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="19" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -1271,11 +1274,11 @@
       </c>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="13" t="s">
         <v>25</v>
       </c>
@@ -1338,11 +1341,11 @@
       </c>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="19">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" s="16">
         <v>45991</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="16">
         <v>45991</v>
       </c>
       <c r="C3" s="8">
@@ -1387,11 +1390,11 @@
       <c r="X3" s="13"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="18">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" s="15">
         <v>46022</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="15">
         <v>46022</v>
       </c>
       <c r="C4" s="8">
@@ -1462,11 +1465,11 @@
       </c>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="18">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" s="15">
         <v>46052</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="15">
         <v>46052</v>
       </c>
       <c r="C5" s="8">
@@ -1537,11 +1540,11 @@
       </c>
       <c r="Y5" s="6"/>
     </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="18">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A6" s="15">
         <v>46079</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="15">
         <v>46079</v>
       </c>
       <c r="C6" s="8">
@@ -1609,6 +1612,80 @@
       </c>
       <c r="X6" s="14">
         <v>161.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A7" s="15">
+        <v>46119</v>
+      </c>
+      <c r="B7" s="15">
+        <v>46119</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="14">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="F7" s="14">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="G7" s="14">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="H7" s="14">
+        <v>74.2</v>
+      </c>
+      <c r="I7" s="14">
+        <v>97.9</v>
+      </c>
+      <c r="J7" s="14">
+        <v>158.5</v>
+      </c>
+      <c r="K7" s="14">
+        <v>102.8</v>
+      </c>
+      <c r="L7" s="14">
+        <v>99.4</v>
+      </c>
+      <c r="M7" s="14">
+        <v>210</v>
+      </c>
+      <c r="N7" s="14">
+        <v>327.5</v>
+      </c>
+      <c r="O7" s="14">
+        <v>302.39999999999998</v>
+      </c>
+      <c r="P7" s="14">
+        <v>298.10000000000002</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>366.5</v>
+      </c>
+      <c r="R7" s="14">
+        <v>423.6</v>
+      </c>
+      <c r="S7" s="14">
+        <v>407</v>
+      </c>
+      <c r="T7" s="14">
+        <v>406.3</v>
+      </c>
+      <c r="U7" s="14">
+        <v>153.6</v>
+      </c>
+      <c r="V7" s="14">
+        <v>211</v>
+      </c>
+      <c r="W7" s="14">
+        <v>169.8</v>
+      </c>
+      <c r="X7" s="14">
+        <v>161.80000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1620,40 +1697,41 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535C5E87-C6BF-4E93-9B61-00AC746AD42A}">
   <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.453125" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="11.625" style="12" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="19" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="11" t="s">
@@ -1698,11 +1776,11 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="11" t="s">
         <v>34</v>
       </c>
@@ -1745,8 +1823,8 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25">
-      <c r="A3" s="18">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" s="15">
         <v>45962</v>
       </c>
       <c r="C3" s="8">
@@ -1797,11 +1875,11 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="18">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" s="15">
         <v>45992</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="15">
         <v>46042</v>
       </c>
       <c r="C4" s="8">
@@ -1852,11 +1930,11 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="18">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" s="15">
         <v>45658</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="15">
         <v>46079</v>
       </c>
       <c r="C5" s="8">
@@ -1896,11 +1974,11 @@
         <v>21064</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="18">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A6" s="15">
         <v>45689</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="15">
         <v>46106</v>
       </c>
       <c r="C6" s="8">
@@ -1955,20 +2033,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1976,19 +2054,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1996,13 +2074,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -2010,31 +2088,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -2042,25 +2120,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>18</v>

--- a/data/industry/TrendForce/TFT LCD.xlsx
+++ b/data/industry/TrendForce/TFT LCD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19ED8C9-CA77-4848-B20D-14335A4E8709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D2580C-BC85-4EEE-8E3C-3FFFCE19456F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Large Size Panel" sheetId="2" r:id="rId1"/>
@@ -24,15 +24,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="36">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -582,13 +579,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9EFAE0-DDA9-4895-A6E7-1B8A3730BEB2}">
-  <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.09765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -868,6 +865,56 @@
         <v>26.7</v>
       </c>
       <c r="P5" s="10">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A6" s="15">
+        <v>46132</v>
+      </c>
+      <c r="B6" s="15">
+        <v>46132</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="10">
+        <v>119</v>
+      </c>
+      <c r="F6" s="10">
+        <v>129</v>
+      </c>
+      <c r="G6" s="10">
+        <v>126</v>
+      </c>
+      <c r="H6" s="10">
+        <v>126</v>
+      </c>
+      <c r="I6" s="10">
+        <v>57.8</v>
+      </c>
+      <c r="J6" s="10">
+        <v>66.2</v>
+      </c>
+      <c r="K6" s="10">
+        <v>63.3</v>
+      </c>
+      <c r="L6" s="10">
+        <v>63.1</v>
+      </c>
+      <c r="M6" s="10">
+        <v>26.2</v>
+      </c>
+      <c r="N6" s="10">
+        <v>27.9</v>
+      </c>
+      <c r="O6" s="10">
+        <v>26.7</v>
+      </c>
+      <c r="P6" s="10">
         <v>26.7</v>
       </c>
     </row>
@@ -887,13 +934,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C2B366-3BE4-4AC7-87BD-872D5D27BEBF}">
   <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.625" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.59765625" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="11.5" style="14" bestFit="1" customWidth="1"/>
@@ -1188,13 +1235,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F72FC54-CD8C-473D-B869-CF3F9FC5C7CC}">
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="24" width="8.875" style="14" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="24" width="8.8984375" style="14" customWidth="1"/>
     <col min="25" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -1704,19 +1751,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535C5E87-C6BF-4E93-9B61-00AC746AD42A}">
   <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.59765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.59765625" style="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="11.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="11.59765625" style="12" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -2033,20 +2080,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.3984375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2054,19 +2101,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -2074,13 +2121,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -2088,31 +2135,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -2120,25 +2167,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>18</v>

--- a/data/industry/TrendForce/TFT LCD.xlsx
+++ b/data/industry/TrendForce/TFT LCD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DEF56D-AFE2-47A2-BB85-A7D03EF200AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F477A41B-E787-4A7D-A8C8-AD8EC18B7988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Large Size Panel" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="36">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -174,24 +174,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -204,7 +204,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -247,7 +247,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -260,39 +260,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -300,8 +300,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -579,18 +579,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9EFAE0-DDA9-4895-A6E7-1B8A3730BEB2}">
-  <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.09765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="25" width="9" style="10"/>
+    <col min="1" max="1" width="12.08984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="9.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
@@ -649,7 +650,7 @@
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="18"/>
@@ -700,7 +701,7 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="15">
         <v>46042</v>
       </c>
@@ -759,7 +760,7 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="15">
         <v>46077</v>
       </c>
@@ -818,7 +819,7 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="15">
         <v>46104</v>
       </c>
@@ -868,7 +869,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="15">
         <v>46132</v>
       </c>
@@ -915,6 +916,56 @@
         <v>26.7</v>
       </c>
       <c r="P6" s="10">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="15">
+        <v>46162</v>
+      </c>
+      <c r="B7" s="15">
+        <v>46162</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="10">
+        <v>119</v>
+      </c>
+      <c r="F7" s="10">
+        <v>129</v>
+      </c>
+      <c r="G7" s="10">
+        <v>126</v>
+      </c>
+      <c r="H7" s="10">
+        <v>126</v>
+      </c>
+      <c r="I7" s="10">
+        <v>57.9</v>
+      </c>
+      <c r="J7" s="10">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="K7" s="10">
+        <v>63.5</v>
+      </c>
+      <c r="L7" s="10">
+        <v>63.3</v>
+      </c>
+      <c r="M7" s="10">
+        <v>26.2</v>
+      </c>
+      <c r="N7" s="10">
+        <v>27.9</v>
+      </c>
+      <c r="O7" s="10">
+        <v>26.7</v>
+      </c>
+      <c r="P7" s="10">
         <v>26.7</v>
       </c>
     </row>
@@ -934,21 +985,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C2B366-3BE4-4AC7-87BD-872D5D27BEBF}">
   <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.59765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.6328125" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="13" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
@@ -999,7 +1050,7 @@
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="18"/>
@@ -1042,7 +1093,7 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="15">
         <v>46022</v>
       </c>
@@ -1093,7 +1144,7 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="15">
         <v>46052</v>
       </c>
@@ -1144,7 +1195,7 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="15">
         <v>46079</v>
       </c>
@@ -1182,7 +1233,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="15">
         <v>46111</v>
       </c>
@@ -1235,18 +1286,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F72FC54-CD8C-473D-B869-CF3F9FC5C7CC}">
   <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="24" width="8.8984375" style="14" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="24" width="8.90625" style="14" customWidth="1"/>
     <col min="25" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
@@ -1321,7 +1372,7 @@
       </c>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="18"/>
@@ -1388,7 +1439,7 @@
       </c>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="16">
         <v>45991</v>
       </c>
@@ -1437,7 +1488,7 @@
       <c r="X3" s="13"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="15">
         <v>46022</v>
       </c>
@@ -1512,7 +1563,7 @@
       </c>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="15">
         <v>46052</v>
       </c>
@@ -1587,7 +1638,7 @@
       </c>
       <c r="Y5" s="6"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="15">
         <v>46079</v>
       </c>
@@ -1661,7 +1712,7 @@
         <v>161.9</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="15">
         <v>46119</v>
       </c>
@@ -1735,7 +1786,7 @@
         <v>161.80000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="15">
         <v>46141</v>
       </c>
@@ -1824,25 +1875,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535C5E87-C6BF-4E93-9B61-00AC746AD42A}">
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.59765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.59765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="11.59765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.453125" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
@@ -1897,7 +1948,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="4"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="18"/>
@@ -1944,7 +1995,7 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="15">
         <v>45962</v>
       </c>
@@ -1996,7 +2047,7 @@
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="15">
         <v>45992</v>
       </c>
@@ -2051,7 +2102,7 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="15">
         <v>45658</v>
       </c>
@@ -2095,7 +2146,7 @@
         <v>21064</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="15">
         <v>45689</v>
       </c>
@@ -2139,7 +2190,7 @@
         <v>18066</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="15">
         <v>45717</v>
       </c>
@@ -2181,6 +2232,50 @@
       </c>
       <c r="N7" s="12">
         <v>22289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" s="15">
+        <v>45748</v>
+      </c>
+      <c r="B8" s="15">
+        <v>46162</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="12">
+        <v>21757</v>
+      </c>
+      <c r="F8" s="12">
+        <v>640</v>
+      </c>
+      <c r="G8" s="12">
+        <v>17526</v>
+      </c>
+      <c r="H8" s="12">
+        <v>1137</v>
+      </c>
+      <c r="I8" s="12">
+        <v>13612</v>
+      </c>
+      <c r="J8" s="12">
+        <v>2650</v>
+      </c>
+      <c r="K8" s="12">
+        <v>19931</v>
+      </c>
+      <c r="L8" s="12">
+        <v>15627</v>
+      </c>
+      <c r="M8" s="12">
+        <v>72827</v>
+      </c>
+      <c r="N8" s="12">
+        <v>20053</v>
       </c>
     </row>
   </sheetData>
@@ -2198,20 +2293,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2219,19 +2314,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -2239,13 +2334,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -2253,31 +2348,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -2285,25 +2380,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
         <v>18</v>

--- a/data/industry/TrendForce/TFT LCD.xlsx
+++ b/data/industry/TrendForce/TFT LCD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F477A41B-E787-4A7D-A8C8-AD8EC18B7988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793F4466-66C2-4ED0-86EC-42B553BC57B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Large Size Panel" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="36">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -300,8 +300,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -580,13 +580,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9EFAE0-DDA9-4895-A6E7-1B8A3730BEB2}">
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="9.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="9.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="9" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -984,17 +984,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C2B366-3BE4-4AC7-87BD-872D5D27BEBF}">
-  <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.6328125" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.6640625" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.44140625" style="14" bestFit="1" customWidth="1"/>
     <col min="13" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -1269,6 +1269,82 @@
       </c>
       <c r="L6" s="14">
         <v>6.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="15">
+        <v>46141</v>
+      </c>
+      <c r="B7" s="15">
+        <v>46141</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="14">
+        <v>1.7</v>
+      </c>
+      <c r="G7" s="14">
+        <v>1.4</v>
+      </c>
+      <c r="H7" s="14">
+        <v>1.4</v>
+      </c>
+      <c r="I7" s="14">
+        <v>5.7</v>
+      </c>
+      <c r="J7" s="14">
+        <v>8.5</v>
+      </c>
+      <c r="K7" s="14">
+        <v>6.4</v>
+      </c>
+      <c r="L7" s="14">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B8" s="15">
+        <v>46171</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1.7</v>
+      </c>
+      <c r="G8" s="14">
+        <v>1.4</v>
+      </c>
+      <c r="H8" s="14">
+        <v>1.4</v>
+      </c>
+      <c r="I8" s="14">
+        <v>5.7</v>
+      </c>
+      <c r="J8" s="14">
+        <v>8.5</v>
+      </c>
+      <c r="K8" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="L8" s="14">
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -1285,14 +1361,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F72FC54-CD8C-473D-B869-CF3F9FC5C7CC}">
-  <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="24" width="8.90625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="24" width="8.88671875" style="14" customWidth="1"/>
     <col min="25" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -1812,13 +1888,13 @@
         <v>74.599999999999994</v>
       </c>
       <c r="I8" s="14">
+        <v>98.4</v>
+      </c>
+      <c r="J8" s="14">
         <v>150</v>
       </c>
-      <c r="J8" s="14">
+      <c r="K8" s="14">
         <v>100.6</v>
-      </c>
-      <c r="K8" s="14">
-        <v>102.8</v>
       </c>
       <c r="L8" s="14">
         <v>102.8</v>
@@ -1858,6 +1934,80 @@
       </c>
       <c r="X8" s="14">
         <v>169.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B9" s="15">
+        <v>46171</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="14">
+        <v>75.5</v>
+      </c>
+      <c r="F9" s="14">
+        <v>75.5</v>
+      </c>
+      <c r="G9" s="14">
+        <v>75.5</v>
+      </c>
+      <c r="H9" s="14">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="I9" s="14">
+        <v>98.9</v>
+      </c>
+      <c r="J9" s="14">
+        <v>142.6</v>
+      </c>
+      <c r="K9" s="14">
+        <v>100.7</v>
+      </c>
+      <c r="L9" s="14">
+        <v>100.6</v>
+      </c>
+      <c r="M9" s="14">
+        <v>201.1</v>
+      </c>
+      <c r="N9" s="14">
+        <v>331.4</v>
+      </c>
+      <c r="O9" s="14">
+        <v>302.8</v>
+      </c>
+      <c r="P9" s="14">
+        <v>317.39999999999998</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>386.9</v>
+      </c>
+      <c r="R9" s="14">
+        <v>437.7</v>
+      </c>
+      <c r="S9" s="14">
+        <v>413.6</v>
+      </c>
+      <c r="T9" s="14">
+        <v>408.9</v>
+      </c>
+      <c r="U9" s="14">
+        <v>152.5</v>
+      </c>
+      <c r="V9" s="14">
+        <v>219.5</v>
+      </c>
+      <c r="W9" s="14">
+        <v>168.5</v>
+      </c>
+      <c r="X9" s="14">
+        <v>168.7</v>
       </c>
     </row>
   </sheetData>
@@ -1876,19 +2026,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535C5E87-C6BF-4E93-9B61-00AC746AD42A}">
   <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.453125" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="11.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="11.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9" style="10"/>
     <col min="26" max="16384" width="9" style="7"/>
   </cols>
@@ -2293,10 +2443,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="27.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
